--- a/data/sqdcp_base.xlsx
+++ b/data/sqdcp_base.xlsx
@@ -483,7 +483,7 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>

--- a/data/sqdcp_base.xlsx
+++ b/data/sqdcp_base.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,6 +656,31 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Acidentes</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>treinametno mensal relacionado a acidentes</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Luis Fernando</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Aberta</t>
         </is>
       </c>
     </row>

--- a/data/sqdcp_base.xlsx
+++ b/data/sqdcp_base.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -684,6 +684,56 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Reclamações</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>laudo automatico expedição</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Rodrigo Maróstica</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Concluída</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Reclamações</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>plano de ação direcionado a maior incidência de reclamações (Vazamento)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Josue/Willian/Julio/Rodrigo</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aberta</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/sqdcp_base.xlsx
+++ b/data/sqdcp_base.xlsx
@@ -629,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,6 +734,56 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Perda</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Desenvolver contadores para prensas Cimep</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Osvaldo/Marcelo J</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aberta</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Perda</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ajustar planta litográfica de verniz para aplicação de verniz CIMEP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Lucas/André/Fernando</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46173</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aberta</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/sqdcp_base.xlsx
+++ b/data/sqdcp_base.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="dados" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="acoes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="metas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -787,4 +788,140 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>indicador</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>unidade</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Acidentes</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>menor_melhor</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Reclamações</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>menor_melhor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Perda</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>menor_melhor</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Atendimento no prazo</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>maior_melhor</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Eficiência</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>75</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>maior_melhor</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/sqdcp_base.xlsx
+++ b/data/sqdcp_base.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -430,50 +430,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>semana</t>
+          <t>acidentes_un</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>acidentes_un</t>
+          <t>reclamacoes_un</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>reclamacoes_un</t>
+          <t>perda_prensas_t</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>perda_prensas_t</t>
+          <t>perda_litografia_t</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>perda_litografia_t</t>
+          <t>perda_montagem_t</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>perda_montagem_t</t>
+          <t>atendimento_prazo_pct</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>atendimento_prazo_pct</t>
+          <t>eficiencia_prensas_pct</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>eficiencia_prensas_pct</t>
+          <t>eficiencia_litografia_pct</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
-        <is>
-          <t>eficiencia_litografia_pct</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>eficiencia_montagem_pct</t>
         </is>
@@ -484,33 +479,30 @@
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
-        <v>15</v>
-      </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>34.5</v>
       </c>
       <c r="G2" t="n">
-        <v>34.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>99.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="I2" t="n">
-        <v>66.8</v>
+        <v>71.3</v>
       </c>
       <c r="J2" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="K2" t="n">
         <v>74.8</v>
       </c>
     </row>
@@ -519,33 +511,30 @@
         <v>46054</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>1.6</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>18.7</v>
       </c>
       <c r="F3" t="n">
-        <v>18.7</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>98.8</v>
       </c>
       <c r="H3" t="n">
-        <v>98.8</v>
+        <v>71.5</v>
       </c>
       <c r="I3" t="n">
-        <v>71.5</v>
+        <v>70</v>
       </c>
       <c r="J3" t="n">
-        <v>70</v>
-      </c>
-      <c r="K3" t="n">
         <v>75</v>
       </c>
     </row>
@@ -554,33 +543,30 @@
         <v>46082</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>10.3</v>
       </c>
       <c r="E4" t="n">
-        <v>10.3</v>
+        <v>17.2</v>
       </c>
       <c r="F4" t="n">
-        <v>17.2</v>
+        <v>30.9</v>
       </c>
       <c r="G4" t="n">
-        <v>30.9</v>
+        <v>98</v>
       </c>
       <c r="H4" t="n">
-        <v>98</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>77.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="K4" t="n">
         <v>79.40000000000001</v>
       </c>
     </row>
@@ -589,33 +575,30 @@
         <v>46113</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>99.23999999999999</v>
+      </c>
+      <c r="H5" t="n">
         <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F5" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>99.23999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -663,25 +646,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Acidentes</t>
+          <t>Reclamações</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>treinametno mensal relacionado a acidentes</t>
+          <t>laudo automatico expedição</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Luis Fernando</t>
+          <t>Rodrigo Maróstica</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46203</v>
+        <v>46122</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aberta</t>
+          <t>Concluída</t>
         </is>
       </c>
     </row>
@@ -693,41 +676,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>laudo automatico expedição</t>
+          <t>plano de ação direcionado a maior incidência de reclamações (Vazamento)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rodrigo Maróstica</t>
+          <t>Josue/Willian/Julio/Rodrigo</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46122</v>
+        <v>46171</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Concluída</t>
+          <t>Aberta</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Reclamações</t>
+          <t>Perda</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>plano de ação direcionado a maior incidência de reclamações (Vazamento)</t>
+          <t>Desenvolver contadores para prensas Cimep</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Josue/Willian/Julio/Rodrigo</t>
+          <t>Osvaldo/Marcelo J</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -743,12 +726,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Desenvolver contadores para prensas Cimep</t>
+          <t>Ajustar planta litográfica de verniz para aplicação de verniz CIMEP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Osvaldo/Marcelo J</t>
+          <t>Lucas/André/Fernando</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
@@ -763,21 +746,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Perda</t>
+          <t>Acidentes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ajustar planta litográfica de verniz para aplicação de verniz CIMEP</t>
+          <t>Treinametno mensal relacionado a acidentes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lucas/André/Fernando</t>
+          <t>Luis Fernando</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>

--- a/data/sqdcp_base.xlsx
+++ b/data/sqdcp_base.xlsx
@@ -646,46 +646,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Reclamações</t>
+          <t>Perda</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>laudo automatico expedição</t>
+          <t>Desenvolver contadores para prensas Cimep</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rodrigo Maróstica</t>
+          <t>Osvaldo/Marcelo J</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46122</v>
+        <v>46173</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Concluída</t>
+          <t>Aberta</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Reclamações</t>
+          <t>Perda</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>plano de ação direcionado a maior incidência de reclamações (Vazamento)</t>
+          <t>Ajustar planta litográfica de verniz para aplicação de verniz CIMEP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Josue/Willian/Julio/Rodrigo</t>
+          <t>Lucas/André/Fernando</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -696,21 +696,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Perda</t>
+          <t>Acidentes</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Desenvolver contadores para prensas Cimep</t>
+          <t>Treinametno mensal relacionado a acidentes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Osvaldo/Marcelo J</t>
+          <t>Luis Fernando</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -721,46 +721,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Perda</t>
+          <t>Reclamações</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ajustar planta litográfica de verniz para aplicação de verniz CIMEP</t>
+          <t>Laudo automatico expedição</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lucas/André/Fernando</t>
+          <t>Rodrigo Maróstica</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46173</v>
+        <v>46122</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aberta</t>
+          <t>Concluída</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Acidentes</t>
+          <t>Reclamações</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Treinametno mensal relacionado a acidentes</t>
+          <t>Plano de ação direcionado a maior incidência de reclamações (Vazamento)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Luis Fernando</t>
+          <t>Josue/Willian/Julio/Rodrigo</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46203</v>
+        <v>46171</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>

--- a/data/sqdcp_base.xlsx
+++ b/data/sqdcp_base.xlsx
@@ -578,7 +578,7 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>1.7</v>
@@ -593,13 +593,13 @@
         <v>99.23999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/data/sqdcp_base.xlsx
+++ b/data/sqdcp_base.xlsx
@@ -596,10 +596,10 @@
         <v>79.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J5" t="n">
-        <v>79</v>
+        <v>74.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/sqdcp_base.xlsx
+++ b/data/sqdcp_base.xlsx
@@ -646,21 +646,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Perda</t>
+          <t>Acidentes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Desenvolver contadores para prensas Cimep</t>
+          <t>Treinametno mensal relacionado a acidentes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Osvaldo/Marcelo J</t>
+          <t>Luis Fernando</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -671,46 +671,46 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Perda</t>
+          <t>Reclamações</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ajustar planta litográfica de verniz para aplicação de verniz CIMEP</t>
+          <t>Laudo automatico expedição</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lucas/André/Fernando</t>
+          <t>Rodrigo Maróstica</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46173</v>
+        <v>46122</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aberta</t>
+          <t>Concluída</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Acidentes</t>
+          <t>Reclamações</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Treinametno mensal relacionado a acidentes</t>
+          <t>Plano de ação direcionado a maior incidência de reclamações (Vazamento)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Luis Fernando</t>
+          <t>Josue/Willian/Julio/Rodrigo</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46203</v>
+        <v>46171</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -721,46 +721,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Reclamações</t>
+          <t>Perda</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Laudo automatico expedição</t>
+          <t>Desenvolver contadores para prensas Cimep</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rodrigo Maróstica</t>
+          <t>Osvaldo/Marcelo J</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46122</v>
+        <v>46173</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Concluída</t>
+          <t>Aberta</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Reclamações</t>
+          <t>Perda</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Plano de ação direcionado a maior incidência de reclamações (Vazamento)</t>
+          <t>Ajustar planta litográfica de verniz para aplicação de verniz CIMEP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Josue/Willian/Julio/Rodrigo</t>
+          <t>Lucas/André/Fernando</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>

--- a/data/sqdcp_base.xlsx
+++ b/data/sqdcp_base.xlsx
@@ -646,25 +646,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Acidentes</t>
+          <t>Reclamações</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Treinametno mensal relacionado a acidentes</t>
+          <t>Laudo automatico expedição</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Luis Fernando</t>
+          <t>Rodrigo Maróstica</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46203</v>
+        <v>46122</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aberta</t>
+          <t>Concluída</t>
         </is>
       </c>
     </row>
@@ -676,41 +676,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Laudo automatico expedição</t>
+          <t>Plano de ação direcionado a maior incidência de reclamações (Vazamento)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rodrigo Maróstica</t>
+          <t>Josue/Willian/Julio/Rodrigo</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46122</v>
+        <v>46171</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Concluída</t>
+          <t>Aberta</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Reclamações</t>
+          <t>Perda</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Plano de ação direcionado a maior incidência de reclamações (Vazamento)</t>
+          <t>Desenvolver contadores para prensas Cimep</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Josue/Willian/Julio/Rodrigo</t>
+          <t>Osvaldo/Marcelo J</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -726,12 +726,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Desenvolver contadores para prensas Cimep</t>
+          <t>Ajustar planta litográfica de verniz para aplicação de verniz CIMEP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Osvaldo/Marcelo J</t>
+          <t>Lucas/André/Fernando</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
@@ -746,21 +746,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Perda</t>
+          <t>Acidentes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ajustar planta litográfica de verniz para aplicação de verniz CIMEP</t>
+          <t>Treinametno mensal relacionado a acidentes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lucas/André/Fernando</t>
+          <t>Luis Fernando</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>

--- a/data/sqdcp_base.xlsx
+++ b/data/sqdcp_base.xlsx
@@ -476,7 +476,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46023</v>
+        <v>46053</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
